--- a/5/food/2026-01-28-sm.xlsx
+++ b/5/food/2026-01-28-sm.xlsx
@@ -835,7 +835,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>МБОУ "Майртупская средняя школа №1"</t>
+          <t>МБОУ "Майртупская средняя школа №1 имени Амхада Абзаиловича Бисултанова"</t>
         </is>
       </c>
       <c r="C1" s="38" t="n"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="J1" s="11" t="inlineStr">
         <is>
-          <t>28.01.2026</t>
+          <t>2026-01-28</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
           <t>Завтрак</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>гор.блюдо</t>
         </is>
@@ -1123,7 +1123,7 @@
           <t>Обед</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>закуска</t>
         </is>
